--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_04-08-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£23.50</t>
+          <t>Error: HTTPSConnectionPool(host='www.building-supplies-online.co.uk', port=443): Max retries exceeded with url: /products/celotex-ga4000-insulation-board-1200-x-2400mm?variant=55597619970432 (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x0000025E30A40450&gt;, 'Connection to www.building-supplies-online.co.uk timed out. (connect timeout=None)'))</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.184); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff616f9e415+77285]
-	GetHandleVerifier [0x0x7ff616f9e470+77376]
-	(No symbol) [0x0x7ff616d69a6a]
-	(No symbol) [0x0x7ff616dc0406]
-	(No symbol) [0x0x7ff616dc06bc]
-	(No symbol) [0x0x7ff616e13ac7]
-	(No symbol) [0x0x7ff616de864f]
-	(No symbol) [0x0x7ff616e1087f]
-	(No symbol) [0x0x7ff616de83e3]
-	(No symbol) [0x0x7ff616db1521]
-	(No symbol) [0x0x7ff616db22b3]
-	GetHandleVerifier [0x0x7ff617281efd+3107021]
-	GetHandleVerifier [0x0x7ff61727c29d+3083373]
-	GetHandleVerifier [0x0x7ff61729bedd+3213485]
-	GetHandleVerifier [0x0x7ff616fb884e+184862]
-	GetHandleVerifier [0x0x7ff616fc055f+216879]
-	GetHandleVerifier [0x0x7ff616fa7084+113236]
-	GetHandleVerifier [0x0x7ff616fa7239+113673]
-	GetHandleVerifier [0x0x7ff616f8e298+11368]
+	GetHandleVerifier [0x0x7ff6e6fee415+77285]
+	GetHandleVerifier [0x0x7ff6e6fee470+77376]
+	(No symbol) [0x0x7ff6e6db9a6a]
+	(No symbol) [0x0x7ff6e6e10406]
+	(No symbol) [0x0x7ff6e6e106bc]
+	(No symbol) [0x0x7ff6e6e63ac7]
+	(No symbol) [0x0x7ff6e6e3864f]
+	(No symbol) [0x0x7ff6e6e6087f]
+	(No symbol) [0x0x7ff6e6e383e3]
+	(No symbol) [0x0x7ff6e6e01521]
+	(No symbol) [0x0x7ff6e6e022b3]
+	GetHandleVerifier [0x0x7ff6e72d1efd+3107021]
+	GetHandleVerifier [0x0x7ff6e72cc29d+3083373]
+	GetHandleVerifier [0x0x7ff6e72ebedd+3213485]
+	GetHandleVerifier [0x0x7ff6e700884e+184862]
+	GetHandleVerifier [0x0x7ff6e701055f+216879]
+	GetHandleVerifier [0x0x7ff6e6ff7084+113236]
+	GetHandleVerifier [0x0x7ff6e6ff7239+113673]
+	GetHandleVerifier [0x0x7ff6e6fde298+11368]
 	BaseThreadInitThunk [0x0x7ff81365e8d7+23]
 	RtlUserThreadStart [0x0x7ff813c5c34c+44]
 </t>
